--- a/exam_forms/010_flamenco_basics_quiz--exam_forms.xlsx
+++ b/exam_forms/010_flamenco_basics_quiz--exam_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>student_name</t>
+          <t>student_first_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>student_email</t>
+          <t>student_last_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>instructor_name</t>
+          <t>student_email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Instructor</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>school_name</t>
+          <t>student_phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>student_phone</t>
+          <t>teacher_first_name</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Teacher First Name</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>teacher_name</t>
+          <t>teacher_last_name</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>teacher</t>
+          <t>Teacher Last Name</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,69 +653,69 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>student_notes</t>
+          <t>school_name</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>School</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>teacher_email</t>
+          <t>student_level</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>teacher_email</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>school_address</t>
+          <t>student_notes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>school_address</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>student_phone</t>
+          <t>school_address</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>student_phone</t>
+          <t>School Address</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,23 +745,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>student_phone</t>
+          <t>teacher_name</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>student_phone</t>
+          <t>Teacher</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>student_name</t>
+          <t>teacher_email</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>student_name</t>
+          <t>Teacher Email</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>student_level</t>
+          <t>school_phone</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>student_level</t>
+          <t>School Phone</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>teacher_name</t>
+          <t>teacher_notes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>teacher</t>
+          <t>Teacher Notes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,41 +842,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>teacher_email</t>
+          <t>school_address2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>teacher_email</t>
+          <t>School Address 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>instructor_name</t>
+          <t>school_address3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>instructor</t>
+          <t>School Address 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>school_address1</t>
+          <t>school_address4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>school_address1</t>
+          <t>School Address 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,18 +911,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>school_address2</t>
+          <t>teacher_phone</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>school_address2</t>
+          <t>Teacher Phone</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -934,156 +934,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>school_address3</t>
+          <t>teacher_phone2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>school_address3</t>
+          <t>Teacher Phone 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>school_address4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>school_address4</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>student_level</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>student_level</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>teacher_level</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>teacher_level</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>student_level</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>student_level</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>teacher_level</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>teacher_level</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>teacher_level</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>teacher_level</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,10 +960,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1177,629 +1039,119 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>teacher_name_choices</t>
+          <t>student_level_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>maria</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>beginner</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>teacher_name_choices</t>
+          <t>student_level_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>juan</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Juan</t>
+          <t>intermediate</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>teacher_name_choices</t>
+          <t>student_level_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>carlos</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>advanced</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>school_address_choices</t>
+          <t>student_level_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>school_address1</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>school_address1</t>
+          <t>master</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>school_address_choices</t>
+          <t>teacher_name_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>school_address2</t>
+          <t>maria</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>school_address2</t>
+          <t>Maria</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>school_address_choices</t>
+          <t>teacher_name_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>school_address3</t>
+          <t>juan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>school_address3</t>
+          <t>Juan</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>school_address_choices</t>
+          <t>teacher_name_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>school_address4</t>
+          <t>carlos</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>school_address4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>student_level_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>beginner</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>beginner</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>student_level_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>student_level_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>advanced</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>advanced</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>student_level_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>master</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>master</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>teacher_name_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>maria</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Maria</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>teacher_name_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>juan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Juan</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>teacher_name_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>carlos</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
           <t>Carlos</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>instructor_name_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>maria</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Maria</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>instructor_name_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>juan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Juan</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>instructor_name_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>carlos</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>student_level_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>beginner</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>beginner</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>student_level_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>student_level_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>advanced</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>advanced</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>student_level_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>master</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>master</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>teacher_level_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>beginner</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>beginner</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>teacher_level_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>teacher_level_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>advanced</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>advanced</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>teacher_level_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>master</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>master</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>student_level_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>beginner</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>beginner</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>student_level_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>student_level_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>advanced</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>advanced</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>student_level_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>master</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>master</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>teacher_level_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>beginner</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>beginner</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>teacher_level_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>teacher_level_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>advanced</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>advanced</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>teacher_level_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>master</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>master</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>teacher_level_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>beginner</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>beginner</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>teacher_level_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>teacher_level_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>advanced</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>advanced</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>teacher_level_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>master</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>master</t>
         </is>
       </c>
     </row>
